--- a/Finanzen/2025/ergebnis_2025.xlsx
+++ b/Finanzen/2025/ergebnis_2025.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>986.61</v>
+        <v>1123.59</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5890.5</v>
+        <v>6164.46</v>
       </c>
     </row>
     <row r="14">
@@ -6659,10 +6659,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="D8" t="n">
         <v>151.69</v>
@@ -6671,7 +6671,7 @@
         <v>164.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>212.27</v>
       </c>
       <c r="D9" t="n">
         <v>598.22</v>
@@ -6709,7 +6709,7 @@
         <v>689.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
       <c r="G9" t="n">
         <v>19</v>
@@ -6773,10 +6773,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
       <c r="C11" t="n">
-        <v>505.75</v>
+        <v>660.85</v>
       </c>
       <c r="D11" t="n">
         <v>237.17</v>
@@ -6785,7 +6785,7 @@
         <v>259.76</v>
       </c>
       <c r="F11" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
       <c r="G11" t="n">
         <v>80.75</v>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5890.5</v>
+        <v>6164.46</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2976.79</v>
@@ -6901,7 +6901,7 @@
         <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>

--- a/Finanzen/2025/ergebnis_2025.xlsx
+++ b/Finanzen/2025/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1123.59</v>
+        <v>1132.82</v>
       </c>
     </row>
     <row r="11">
@@ -6817,13 +6817,13 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
       <c r="E12" t="n">
         <v>740.48</v>
       </c>
       <c r="F12" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
@@ -6895,13 +6895,13 @@
         <v>6164.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
